--- a/docs/qa/Mill-Smart-Log-Test-Case-Blackbox.xlsx
+++ b/docs/qa/Mill-Smart-Log-Test-Case-Blackbox.xlsx
@@ -73714,7 +73714,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1">
+    <row r="8" ht="94.5" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>K-2</t>
@@ -73722,12 +73722,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Nama kolom shell_loss_percent vs standar "Shell Bin Kernel Loss" pada Kernel Plant</t>
+          <t>SELESAI 2026-10-08 — penamaan Shell Bin Kernel Loss pada Kernel Plant sudah seragam</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Kemungkinan dua kuantitas berbeda. Keputusan penamaan belum diambil; tabelnya masih kosong.</t>
+          <t>Kolom yang dulu bernama shell_loss_percent kini "Shell Bin Kernel Loss" di Form, Detail, Data Preview, Laporan, dan header ekspor CSV — mengikuti nama standar di master. Nama lamanya menyebut zat yang salah: kehilangan SHELL, padahal yang diukur KERNEL yang terbuang ke shell bin. Angkanya tidak pernah salah dan tidak berubah, hanya namanya. Yang diperiksa QA: label barunya konsisten di kelima tempat itu, dan header CSV berbunyi "Shell Bin Kernel Loss (%)".</t>
         </is>
       </c>
     </row>
